--- a/output/yearly_surface_area_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_72_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633077524</v>
+        <v>10.8449761361512</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907193689248</v>
+        <v>37.78907125872946</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.019496085364694</v>
+        <v>6.510950774564847</v>
       </c>
       <c r="C2" t="n">
-        <v>7.65174160689964</v>
+        <v>5.603815895840794</v>
       </c>
       <c r="D2" t="n">
-        <v>27.75891633757856</v>
+        <v>28.48148264790422</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.8234907018806</v>
+        <v>18.30959468420301</v>
       </c>
       <c r="C3" t="n">
-        <v>32.22095965338032</v>
+        <v>25.07874510498477</v>
       </c>
       <c r="D3" t="n">
-        <v>84.75427930762714</v>
+        <v>81.45560702135786</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.5073522455799</v>
+        <v>33.83397113145782</v>
       </c>
       <c r="C4" t="n">
-        <v>70.51402885752717</v>
+        <v>59.52532680389261</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2188512603809</v>
+        <v>90.99819470663685</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.59713325502288</v>
+        <v>45.50400609183966</v>
       </c>
       <c r="C5" t="n">
-        <v>118.1042488208913</v>
+        <v>98.76381904722915</v>
       </c>
       <c r="D5" t="n">
-        <v>76.96902001294994</v>
+        <v>61.06470720415162</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.96739100824416</v>
+        <v>42.9082651618111</v>
       </c>
       <c r="C6" t="n">
-        <v>128.8858021089298</v>
+        <v>98.69706020334036</v>
       </c>
       <c r="D6" t="n">
-        <v>49.22777513404782</v>
+        <v>43.75354993516761</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>29.8235317596096</v>
       </c>
       <c r="C7" t="n">
-        <v>118.6952609388479</v>
+        <v>85.87739868128548</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.1890196430299</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>78.85888434362504</v>
+        <v>60.24985660962675</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
         <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.654647911257646</v>
+        <v>7.710367017717741</v>
       </c>
       <c r="C21" t="n">
-        <v>92.81260592399894</v>
+        <v>96.37958772147176</v>
       </c>
       <c r="D21" t="n">
-        <v>7.654647911257646</v>
+        <v>8.674162894932458</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.390015880493241</v>
+        <v>7.905032514595318</v>
       </c>
       <c r="C2" t="n">
-        <v>8.055239913345078</v>
+        <v>4.293182710671302</v>
       </c>
       <c r="D2" t="n">
-        <v>24.82643594499334</v>
+        <v>33.26161221988194</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.92028281397354</v>
+        <v>20.08655802888974</v>
       </c>
       <c r="C3" t="n">
-        <v>30.77288178961627</v>
+        <v>23.22815068247953</v>
       </c>
       <c r="D3" t="n">
-        <v>86.10909113948775</v>
+        <v>84.26831419402498</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.55840312620073</v>
+        <v>34.44658169890783</v>
       </c>
       <c r="C4" t="n">
-        <v>75.14689627386785</v>
+        <v>60.49529353568845</v>
       </c>
       <c r="D4" t="n">
-        <v>122.7263170124853</v>
+        <v>107.0664593820444</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.56754195517523</v>
+        <v>47.93383165985053</v>
       </c>
       <c r="C5" t="n">
-        <v>122.2275891787279</v>
+        <v>104.2370624984051</v>
       </c>
       <c r="D5" t="n">
-        <v>95.35224577497146</v>
+        <v>77.77896186895356</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.63407981488576</v>
+        <v>51.76362945411734</v>
       </c>
       <c r="C6" t="n">
-        <v>155.6531532652191</v>
+        <v>125.8669279183708</v>
       </c>
       <c r="D6" t="n">
-        <v>59.16993413495527</v>
+        <v>51.36111289537615</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>40.36357511240336</v>
+      </c>
+      <c r="C7" t="n">
+        <v>113.9043321421234</v>
+      </c>
+      <c r="D7" t="n">
         <v>41.98051358129786</v>
-      </c>
-      <c r="C7" t="n">
-        <v>148.2193596486622</v>
-      </c>
-      <c r="D7" t="n">
-        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.45042657426681</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="C8" t="n">
-        <v>113.6569317206532</v>
+        <v>85.78511439708629</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>67.44999427257284</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.82524989499308</v>
+        <v>7.896670183085952</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7500923980359</v>
+        <v>105.6179636987746</v>
       </c>
       <c r="D21" t="n">
-        <v>8.803406131867215</v>
+        <v>9.87083772885744</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.40612475438869</v>
+        <v>8.069966128908781</v>
       </c>
       <c r="C2" t="n">
-        <v>10.18955942237764</v>
+        <v>10.27300797723862</v>
       </c>
       <c r="D2" t="n">
-        <v>26.0398761074424</v>
+        <v>30.00810032800801</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.12292375167588</v>
+        <v>22.76672926148353</v>
       </c>
       <c r="C3" t="n">
-        <v>30.68943323475529</v>
+        <v>19.88529974951915</v>
       </c>
       <c r="D3" t="n">
-        <v>85.15679586636833</v>
+        <v>89.24086631603507</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.84819862540279</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="C4" t="n">
-        <v>74.86611643045326</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="D4" t="n">
-        <v>133.5618664242573</v>
+        <v>121.0161125116873</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.00365892003907</v>
+        <v>49.33282213840224</v>
       </c>
       <c r="C5" t="n">
-        <v>127.4799393964484</v>
+        <v>107.4031988446011</v>
       </c>
       <c r="D5" t="n">
-        <v>110.42207303516</v>
+        <v>93.09422605520381</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.73095404243671</v>
+        <v>57.9623844587317</v>
       </c>
       <c r="C6" t="n">
-        <v>171.9148222383632</v>
+        <v>142.4908617943821</v>
       </c>
       <c r="D6" t="n">
-        <v>71.44668917656163</v>
+        <v>61.62528514327655</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.04146405441917</v>
+        <v>49.46633982617978</v>
       </c>
       <c r="C7" t="n">
-        <v>178.5219842879443</v>
+        <v>144.745936271037</v>
       </c>
       <c r="D7" t="n">
-        <v>48.68781389671206</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.04562772494764</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="C8" t="n">
-        <v>147.0363536650448</v>
+        <v>114.1576230498191</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.41874860582365</v>
+        <v>16.52968609640354</v>
       </c>
       <c r="C9" t="n">
-        <v>97.07030425740334</v>
+        <v>78.65468082114168</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>55.94489292650449</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
+        <v>37.49392657288993</v>
+      </c>
+      <c r="D11" t="n">
         <v>37.31623023842126</v>
-      </c>
-      <c r="D11" t="n">
-        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.980037741825059</v>
+        <v>8.067569185127303</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7305095146383</v>
+        <v>113.9544147399232</v>
       </c>
       <c r="D21" t="n">
-        <v>9.975047177281324</v>
+        <v>11.09290762955004</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.690430677992765</v>
+        <v>7.39648720379547</v>
       </c>
       <c r="C2" t="n">
-        <v>7.091163667774712</v>
+        <v>6.902668108559324</v>
       </c>
       <c r="D2" t="n">
-        <v>21.64851862634641</v>
+        <v>24.45140832197106</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.32127784566274</v>
+        <v>26.38937829015427</v>
       </c>
       <c r="C3" t="n">
-        <v>47.19752088166541</v>
+        <v>34.53297549688155</v>
       </c>
       <c r="D3" t="n">
-        <v>93.44274649021142</v>
+        <v>97.29610622938014</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.26040948799944</v>
+        <v>23.70037132822225</v>
       </c>
       <c r="C4" t="n">
-        <v>103.1610670145506</v>
+        <v>86.79925977557325</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8742010629281</v>
+        <v>113.1542768960789</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.01188845010476</v>
+        <v>32.64311116620645</v>
       </c>
       <c r="C5" t="n">
-        <v>102.7153535568226</v>
+        <v>85.14206965080464</v>
       </c>
       <c r="D5" t="n">
-        <v>72.35480580298994</v>
+        <v>62.73367830137119</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28182801104362</v>
+        <v>30.71201343195298</v>
       </c>
       <c r="C6" t="n">
-        <v>117.5750868083023</v>
+        <v>95.31592110991434</v>
       </c>
       <c r="D6" t="n">
-        <v>32.04031807579891</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="C7" t="n">
-        <v>103.3642887893297</v>
+        <v>80.24805734513427</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>71.5154115158589</v>
+        <v>57.91329707351935</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
+        <v>29.32480392585223</v>
+      </c>
+      <c r="D10" t="n">
         <v>29.18245050873644</v>
-      </c>
-      <c r="D10" t="n">
-        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.457535487908019</v>
+        <v>4.501313223971626</v>
       </c>
       <c r="C2" t="n">
-        <v>3.704134088123216</v>
+        <v>3.53036474447153</v>
       </c>
       <c r="D2" t="n">
-        <v>15.38202303013903</v>
+        <v>17.21298249855933</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.86123908299849</v>
+        <v>26.74280746368311</v>
       </c>
       <c r="C3" t="n">
-        <v>38.19489443372216</v>
+        <v>31.20485077948487</v>
       </c>
       <c r="D3" t="n">
-        <v>90.96874227550944</v>
+        <v>95.08226515630359</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.74685762768712</v>
+        <v>35.39102299039327</v>
       </c>
       <c r="C4" t="n">
-        <v>113.7924129038393</v>
+        <v>89.76021085158163</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9387186739679</v>
+        <v>133.357662901774</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.99425804915732</v>
+        <v>36.03014074585795</v>
       </c>
       <c r="C5" t="n">
-        <v>142.1570675749382</v>
+        <v>121.9821522526662</v>
       </c>
       <c r="D5" t="n">
-        <v>93.65873098514572</v>
+        <v>81.33779729684825</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>36.58875518957439</v>
       </c>
       <c r="C6" t="n">
-        <v>141.8468353003962</v>
+        <v>115.8845172615893</v>
       </c>
       <c r="D6" t="n">
-        <v>40.05039759474864</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>129.654510561355</v>
+        <v>104.7416808183879</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>75.8547363686298</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>46.37187106239383</v>
+        <v>44.04218376021615</v>
       </c>
       <c r="D9" t="n">
         <v>28.51093507903161</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.339725763398402</v>
+        <v>4.602433237509047</v>
       </c>
       <c r="C2" t="n">
-        <v>5.802128932098649</v>
+        <v>5.714753386420683</v>
       </c>
       <c r="D2" t="n">
-        <v>14.04586440465912</v>
+        <v>16.39420491321749</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.72531593145592</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="C3" t="n">
-        <v>25.74142480535137</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="D3" t="n">
-        <v>82.94295479329178</v>
+        <v>87.23810099937157</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.39172700065703</v>
+        <v>43.55916388972673</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4628644703819</v>
+        <v>84.36158022592842</v>
       </c>
       <c r="D4" t="n">
-        <v>152.2464887314826</v>
+        <v>148.966469651594</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.19814277647117</v>
+        <v>44.1541029985003</v>
       </c>
       <c r="C5" t="n">
-        <v>175.8801012158161</v>
+        <v>143.7278639017331</v>
       </c>
       <c r="D5" t="n">
-        <v>118.055161435679</v>
+        <v>107.4277425372073</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>42.50574860306991</v>
       </c>
       <c r="C6" t="n">
-        <v>179.924901757313</v>
+        <v>154.606610212492</v>
       </c>
       <c r="D6" t="n">
-        <v>55.8692983532775</v>
+        <v>51.80388110999145</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="C7" t="n">
-        <v>165.1672702670749</v>
+        <v>134.5053259680385</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>128.8445687053514</v>
+        <v>106.814150222053</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.217187226816798</v>
+        <v>2.713550654538184</v>
       </c>
       <c r="C2" t="n">
-        <v>2.789145227765188</v>
+        <v>2.582978209873358</v>
       </c>
       <c r="D2" t="n">
-        <v>9.798823836087415</v>
+        <v>11.30875180521901</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.51424017504286</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C3" t="n">
-        <v>26.07031028627405</v>
+        <v>23.30178176029805</v>
       </c>
       <c r="D3" t="n">
-        <v>79.76209223153211</v>
+        <v>84.55302102825655</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.80762817435918</v>
+        <v>48.08992954482576</v>
       </c>
       <c r="C4" t="n">
-        <v>100.4170821811807</v>
+        <v>81.71969715380025</v>
       </c>
       <c r="D4" t="n">
-        <v>160.9889520378005</v>
+        <v>159.061781294364</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.327152636355</v>
+        <v>46.2157731774186</v>
       </c>
       <c r="C5" t="n">
-        <v>210.0940087088175</v>
+        <v>167.8297700409923</v>
       </c>
       <c r="D5" t="n">
-        <v>124.2892593576462</v>
+        <v>117.2206758870692</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.95102009244145</v>
+        <v>36.30699359845555</v>
       </c>
       <c r="C6" t="n">
-        <v>212.0457231448601</v>
+        <v>188.7400143937451</v>
       </c>
       <c r="D6" t="n">
-        <v>54.33973543006097</v>
+        <v>51.07935130425731</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.222537933694536</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>170.2576321135946</v>
+        <v>141.2725128934118</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>93.37893288943536</v>
+        <v>83.28165775125692</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.878885179479147</v>
+        <v>4.009457624143973</v>
       </c>
       <c r="C2" t="n">
-        <v>7.035204048632643</v>
+        <v>3.002184479586747</v>
       </c>
       <c r="D2" t="n">
-        <v>8.211337798320322</v>
+        <v>16.20767284941059</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09361018926871</v>
+        <v>15.11891464540088</v>
       </c>
       <c r="C3" t="n">
-        <v>18.47649179392497</v>
+        <v>16.33137306014569</v>
       </c>
       <c r="D3" t="n">
-        <v>70.98035901704439</v>
+        <v>75.0595207281899</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.42550733322892</v>
+        <v>44.10796085640069</v>
       </c>
       <c r="C4" t="n">
-        <v>84.24671574453154</v>
+        <v>70.45021525675112</v>
       </c>
       <c r="D4" t="n">
-        <v>163.2096653448067</v>
+        <v>164.141343916137</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.20629985774141</v>
+        <v>57.75130870231863</v>
       </c>
       <c r="C5" t="n">
-        <v>198.3866673356742</v>
+        <v>161.0066234964769</v>
       </c>
       <c r="D5" t="n">
-        <v>147.1885245592031</v>
+        <v>142.6233977344554</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.83154997215961</v>
+        <v>47.25544399621598</v>
       </c>
       <c r="C6" t="n">
-        <v>268.9615645508647</v>
+        <v>226.174054356676</v>
       </c>
       <c r="D6" t="n">
-        <v>74.22405343187586</v>
+        <v>71.20517924131691</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="C7" t="n">
-        <v>227.3295714045744</v>
+        <v>201.3986692923034</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>145.8680738969911</v>
+        <v>127.0921490532708</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>61.4593697812588</v>
+        <v>58.90780749792134</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>21.69662426385451</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.787181732356694</v>
+        <v>2.805834938737384</v>
       </c>
       <c r="C2" t="n">
-        <v>3.388993075059989</v>
+        <v>1.91146278016854</v>
       </c>
       <c r="D2" t="n">
-        <v>7.124543089719102</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.21847207415731</v>
+        <v>14.65749322440488</v>
       </c>
       <c r="C3" t="n">
-        <v>22.84526907782328</v>
+        <v>14.29915531235479</v>
       </c>
       <c r="D3" t="n">
-        <v>64.2062998577414</v>
+        <v>71.69212610262333</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.12897846881738</v>
+        <v>38.93905919354124</v>
       </c>
       <c r="C4" t="n">
-        <v>70.66718149938967</v>
+        <v>59.18073335970198</v>
       </c>
       <c r="D4" t="n">
-        <v>162.4694275758046</v>
+        <v>164.8943444052943</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.36676670189014</v>
+        <v>63.2245521534946</v>
       </c>
       <c r="C5" t="n">
-        <v>187.39109304811</v>
+        <v>154.2816517223863</v>
       </c>
       <c r="D5" t="n">
-        <v>163.1173810606076</v>
+        <v>160.9575361112646</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.80766923208819</v>
+        <v>55.90955000915161</v>
       </c>
       <c r="C6" t="n">
-        <v>297.1377236627482</v>
+        <v>247.6684385934556</v>
       </c>
       <c r="D6" t="n">
-        <v>87.62785483795757</v>
+        <v>85.77627866774809</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>283.4433249362094</v>
+        <v>249.547503699384</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>186.5075201142878</v>
+        <v>165.0612415150162</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>69.44686910301085</v>
+        <v>70.9999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.259803288726911</v>
+        <v>4.080143458849744</v>
       </c>
       <c r="C2" t="n">
-        <v>4.995132319207771</v>
+        <v>7.494661974220151</v>
       </c>
       <c r="D2" t="n">
-        <v>15.15523931045801</v>
+        <v>19.03117924682442</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.99343086570654</v>
+        <v>12.12949288596934</v>
       </c>
       <c r="C3" t="n">
-        <v>18.46176557836127</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D3" t="n">
-        <v>56.6664774891259</v>
+        <v>66.0667117572891</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.32644862609123</v>
+        <v>33.56595400819845</v>
       </c>
       <c r="C4" t="n">
-        <v>64.54107582488956</v>
+        <v>48.23031946653305</v>
       </c>
       <c r="D4" t="n">
-        <v>158.1683908834994</v>
+        <v>161.3845963626119</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.90043654237292</v>
+        <v>62.04645490839843</v>
       </c>
       <c r="C5" t="n">
-        <v>163.2155558310322</v>
+        <v>133.9594742444773</v>
       </c>
       <c r="D5" t="n">
-        <v>178.2117520134023</v>
+        <v>178.5308200172825</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.64794745593223</v>
+        <v>67.30076862152737</v>
       </c>
       <c r="C6" t="n">
-        <v>298.5062799624682</v>
+        <v>250.0432862900287</v>
       </c>
       <c r="D6" t="n">
-        <v>108.9209807953666</v>
+        <v>108.5989675483737</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.2551408965797</v>
+        <v>36.05173919535137</v>
       </c>
       <c r="C7" t="n">
-        <v>340.8146972769845</v>
+        <v>294.8816674383889</v>
       </c>
       <c r="D7" t="n">
-        <v>53.83806235319084</v>
+        <v>54.73636150257666</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>259.6919027273663</v>
+        <v>231.1524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>125.3593643552752</v>
+        <v>122.4749896001981</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>51.53193699591508</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.979244429490575</v>
+        <v>5.380959166976768</v>
       </c>
       <c r="C2" t="n">
-        <v>7.184429699678158</v>
+        <v>5.542947538177491</v>
       </c>
       <c r="D2" t="n">
-        <v>7.149086782325274</v>
+        <v>7.450483327529043</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.082687791334985</v>
+        <v>2.88731999818987</v>
       </c>
       <c r="C2" t="n">
-        <v>2.916772429317273</v>
+        <v>4.196971435655114</v>
       </c>
       <c r="D2" t="n">
-        <v>11.27635413097886</v>
+        <v>14.00659449648924</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5438314748905</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C3" t="n">
-        <v>21.51990967709008</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D3" t="n">
-        <v>62.72876956284995</v>
+        <v>73.68507394224436</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.15672944644354</v>
+        <v>46.91575929054657</v>
       </c>
       <c r="C4" t="n">
-        <v>92.98917905084939</v>
+        <v>70.29706261488862</v>
       </c>
       <c r="D4" t="n">
-        <v>163.4521570277557</v>
+        <v>165.4686668122787</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.65064635267094</v>
+        <v>40.20256848890689</v>
       </c>
       <c r="C5" t="n">
-        <v>249.4620916491146</v>
+        <v>206.7560665143783</v>
       </c>
       <c r="D5" t="n">
-        <v>161.4974973486003</v>
+        <v>162.7001382863027</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.25287430153496</v>
+        <v>22.37992066601029</v>
       </c>
       <c r="C6" t="n">
-        <v>280.0710215721216</v>
+        <v>245.6558557997497</v>
       </c>
       <c r="D6" t="n">
-        <v>83.11966938005622</v>
+        <v>84.20646408865744</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>182.59427376516</v>
+        <v>162.5322594288764</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>92.37755023110363</v>
+        <v>90.20788780471817</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>39.2718716652809</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.200137662946108</v>
+        <v>5.990624491314037</v>
       </c>
       <c r="C2" t="n">
-        <v>9.600510799829559</v>
+        <v>3.872994693253667</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68287979599506</v>
+        <v>9.078221021170256</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.8194815956056</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C3" t="n">
-        <v>18.10342766631118</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="D3" t="n">
-        <v>9.140071126537805</v>
+        <v>9.395325529641976</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39834319597653</v>
+        <v>13.3988483414613</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14426732011242</v>
+        <v>70.14691190529739</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576275670114886</v>
+        <v>1.576335098995447</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.299474107524283</v>
+        <v>5.859070298944964</v>
       </c>
       <c r="C2" t="n">
-        <v>5.355433726666351</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D2" t="n">
-        <v>29.48875579246144</v>
+        <v>19.88039101099791</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.87195619228719</v>
+        <v>16.98914402199105</v>
       </c>
       <c r="C3" t="n">
-        <v>30.19855938263188</v>
+        <v>14.7753029489145</v>
       </c>
       <c r="D3" t="n">
-        <v>25.14255870576082</v>
+        <v>14.75075925630833</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.17862132891069</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="C4" t="n">
-        <v>28.12903522207961</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="D4" t="n">
-        <v>19.85879256150448</v>
+        <v>19.99918248321178</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43927262147843</v>
+        <v>15.44491676973904</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13488936193232</v>
+        <v>86.16637776801782</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250373183469144</v>
+        <v>3.251561425208219</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.959208564778139</v>
+        <v>5.451645001682538</v>
       </c>
       <c r="C2" t="n">
-        <v>4.838052686528282</v>
+        <v>5.568472978487908</v>
       </c>
       <c r="D2" t="n">
-        <v>27.78738702100172</v>
+        <v>21.79676252968769</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.45333075965055</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C3" t="n">
-        <v>24.59768872990384</v>
+        <v>16.80752069670539</v>
       </c>
       <c r="D3" t="n">
-        <v>42.89746593706438</v>
+        <v>27.22877257728529</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.40079940970673</v>
+        <v>24.33850733598268</v>
       </c>
       <c r="C4" t="n">
-        <v>55.326391872829</v>
+        <v>30.82196917482861</v>
       </c>
       <c r="D4" t="n">
-        <v>27.98864530037232</v>
+        <v>22.90908267859932</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.72621556370216</v>
+        <v>12.00186568441726</v>
       </c>
       <c r="C5" t="n">
-        <v>31.95588777323368</v>
+        <v>26.35992585902687</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72759976641282</v>
+        <v>16.74301881252666</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0383585751182</v>
+        <v>102.1324147564126</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181899941603205</v>
+        <v>5.022905643757999</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.539421457988005</v>
+        <v>5.027529993447916</v>
       </c>
       <c r="C2" t="n">
-        <v>9.525897974306801</v>
+        <v>6.734789251133119</v>
       </c>
       <c r="D2" t="n">
-        <v>32.394728997032</v>
+        <v>24.1460847859503</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.91475218064655</v>
+        <v>18.76610736667778</v>
       </c>
       <c r="C3" t="n">
-        <v>21.26956401250715</v>
+        <v>19.63004534641497</v>
       </c>
       <c r="D3" t="n">
-        <v>54.47227137013428</v>
+        <v>37.7383817512474</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.06370009425158</v>
+        <v>30.83473189498382</v>
       </c>
       <c r="C4" t="n">
-        <v>58.19800390775092</v>
+        <v>37.21609197258809</v>
       </c>
       <c r="D4" t="n">
-        <v>42.37223091529233</v>
+        <v>30.71986741358695</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.16419821298325</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>69.87589284976674</v>
+        <v>43.17235529425349</v>
       </c>
       <c r="D5" t="n">
-        <v>32.7658296292373</v>
+        <v>31.3668391506856</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.7597749120958</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>32.16107304342126</v>
+        <v>27.69313924139403</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04525636680019</v>
+        <v>18.07608686019915</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7238153453155</v>
+        <v>117.9249476117754</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015085455600063</v>
+        <v>6.886128327694913</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.031097131366408</v>
+        <v>6.043638867343365</v>
       </c>
       <c r="C2" t="n">
-        <v>9.590693322787089</v>
+        <v>8.514697838932587</v>
       </c>
       <c r="D2" t="n">
-        <v>34.45934441906304</v>
+        <v>32.9965403397353</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.85446466005999</v>
+        <v>15.98776136365931</v>
       </c>
       <c r="C3" t="n">
-        <v>28.25960766674444</v>
+        <v>22.0549621759046</v>
       </c>
       <c r="D3" t="n">
-        <v>63.00856765856029</v>
+        <v>44.87077882260047</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.29120351972959</v>
+        <v>24.87454158250144</v>
       </c>
       <c r="C4" t="n">
-        <v>46.31591144325178</v>
+        <v>36.87149852839745</v>
       </c>
       <c r="D4" t="n">
-        <v>51.66349118828415</v>
+        <v>36.46309148343079</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.93639168786899</v>
+        <v>21.74571164906685</v>
       </c>
       <c r="C5" t="n">
-        <v>66.07162049581035</v>
+        <v>42.21515128261285</v>
       </c>
       <c r="D5" t="n">
-        <v>32.2749557771139</v>
+        <v>28.74066404182538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.36984114706057</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>49.06676851055134</v>
+        <v>33.56988099901544</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>21.55917958525995</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048532058786732</v>
+        <v>7.068191723897331</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07998805112561</v>
+        <v>67.14782137702464</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405332536741708</v>
+        <v>5.301143792922998</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.30714816270901</v>
+        <v>4.587707021945345</v>
       </c>
       <c r="C2" t="n">
-        <v>5.820782138479339</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D2" t="n">
-        <v>27.47322775564274</v>
+        <v>31.55926170071797</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.49246179910018</v>
+        <v>19.31588608105599</v>
       </c>
       <c r="C3" t="n">
-        <v>34.09118902997049</v>
+        <v>29.41806995775567</v>
       </c>
       <c r="D3" t="n">
-        <v>76.72849182540946</v>
+        <v>62.63550353094651</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.91505528028281</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="C4" t="n">
-        <v>61.51631114810513</v>
+        <v>48.67701467196535</v>
       </c>
       <c r="D4" t="n">
-        <v>72.69645400406782</v>
+        <v>52.28886447588937</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.50214040742241</v>
+        <v>31.21957699504858</v>
       </c>
       <c r="C5" t="n">
-        <v>77.92622402459058</v>
+        <v>57.99674562838034</v>
       </c>
       <c r="D5" t="n">
-        <v>43.85957868722626</v>
+        <v>36.20194659410114</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.15728492132452</v>
+        <v>22.21891404251382</v>
       </c>
       <c r="C6" t="n">
-        <v>81.46935148921733</v>
+        <v>54.017722183068</v>
       </c>
       <c r="D6" t="n">
-        <v>34.69692736349078</v>
+        <v>32.92585450502953</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>49.52622643613884</v>
+        <v>37.24947139453248</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>24.70077223884975</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.265233797855702</v>
+        <v>7.294809747183997</v>
       </c>
       <c r="C21" t="n">
-        <v>75.37680065275292</v>
+        <v>77.50735356382997</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448925348391777</v>
+        <v>6.382958528785998</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.120616098902116</v>
+        <v>5.6018524004323</v>
       </c>
       <c r="C2" t="n">
-        <v>9.434595437811847</v>
+        <v>6.958627727701391</v>
       </c>
       <c r="D2" t="n">
-        <v>29.66056164070464</v>
+        <v>32.13162061229386</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.76596849795754</v>
+        <v>17.40147805777471</v>
       </c>
       <c r="C3" t="n">
-        <v>27.34167356327367</v>
+        <v>22.47220495020949</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54258165640833</v>
+        <v>73.35127972280044</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.30390948662256</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="C4" t="n">
-        <v>74.48323482579701</v>
+        <v>63.67321085433538</v>
       </c>
       <c r="D4" t="n">
-        <v>92.91260272991813</v>
+        <v>71.42018198854697</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.82245220091413</v>
+        <v>38.31270415823178</v>
       </c>
       <c r="C5" t="n">
-        <v>98.00296457643788</v>
+        <v>76.60086462385739</v>
       </c>
       <c r="D5" t="n">
-        <v>60.0093284220863</v>
+        <v>47.44295780772712</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>33.48937768726721</v>
       </c>
       <c r="C6" t="n">
-        <v>104.5738019609618</v>
+        <v>74.94858323761002</v>
       </c>
       <c r="D6" t="n">
-        <v>40.29190752999335</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>85.99717190120359</v>
+        <v>60.42558944868693</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>46.14705083812132</v>
+        <v>38.21943812632832</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.467857739989295</v>
+        <v>7.50946312279659</v>
       </c>
       <c r="C21" t="n">
-        <v>84.01339957487957</v>
+        <v>87.29750880251035</v>
       </c>
       <c r="D21" t="n">
-        <v>6.534375522490634</v>
+        <v>7.50946312279659</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_72_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449761361512</v>
+        <v>10.84497631308466</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907125872946</v>
+        <v>37.78907187525007</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.510950774564847</v>
+        <v>9.233337158441252</v>
       </c>
       <c r="C2" t="n">
-        <v>5.603815895840794</v>
+        <v>9.558295648546945</v>
       </c>
       <c r="D2" t="n">
-        <v>28.48148264790422</v>
+        <v>15.11204241147115</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.30959468420301</v>
+        <v>22.70782439922873</v>
       </c>
       <c r="C3" t="n">
-        <v>25.07874510498477</v>
+        <v>29.52606220522282</v>
       </c>
       <c r="D3" t="n">
-        <v>81.45560702135786</v>
+        <v>55.92525797241955</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.83397113145782</v>
+        <v>41.03214529899544</v>
       </c>
       <c r="C4" t="n">
-        <v>59.52532680389261</v>
+        <v>61.74604011089889</v>
       </c>
       <c r="D4" t="n">
-        <v>90.99819470663685</v>
+        <v>73.23248825058657</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.50400609183966</v>
+        <v>52.20443417332415</v>
       </c>
       <c r="C5" t="n">
-        <v>98.76381904722915</v>
+        <v>82.76133146800613</v>
       </c>
       <c r="D5" t="n">
-        <v>61.06470720415162</v>
+        <v>53.97158004096841</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.9082651618111</v>
+        <v>49.22777513404782</v>
       </c>
       <c r="C6" t="n">
-        <v>98.69706020334036</v>
+        <v>84.89074223851746</v>
       </c>
       <c r="D6" t="n">
-        <v>43.75354993516761</v>
+        <v>41.33845058272045</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.8235317596096</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="C7" t="n">
-        <v>85.87739868128548</v>
+        <v>82.16442886382406</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>19.77730750205199</v>
       </c>
       <c r="C8" t="n">
-        <v>60.24985660962675</v>
+        <v>60.75054793879262</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>9.207811718130833</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.710367017717741</v>
+        <v>7.717776224367244</v>
       </c>
       <c r="C21" t="n">
-        <v>96.37958772147176</v>
+        <v>96.47220280459055</v>
       </c>
       <c r="D21" t="n">
-        <v>8.674162894932458</v>
+        <v>8.682498252413149</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.905032514595318</v>
+        <v>10.29853341754904</v>
       </c>
       <c r="C2" t="n">
-        <v>4.293182710671302</v>
+        <v>9.351146882950868</v>
       </c>
       <c r="D2" t="n">
-        <v>33.26161221988194</v>
+        <v>25.58434517267188</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08655802888974</v>
+        <v>27.27785996249763</v>
       </c>
       <c r="C3" t="n">
-        <v>23.22815068247953</v>
+        <v>33.48250545333747</v>
       </c>
       <c r="D3" t="n">
-        <v>84.26831419402498</v>
+        <v>54.90424036000287</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.44658169890783</v>
+        <v>41.90001026954963</v>
       </c>
       <c r="C4" t="n">
-        <v>60.49529353568845</v>
+        <v>67.36163697919065</v>
       </c>
       <c r="D4" t="n">
-        <v>107.0664593820444</v>
+        <v>83.46818981506382</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.93383165985053</v>
+        <v>56.69592992025331</v>
       </c>
       <c r="C5" t="n">
-        <v>104.2370624984051</v>
+        <v>98.6411005841983</v>
       </c>
       <c r="D5" t="n">
-        <v>77.77896186895356</v>
+        <v>65.97344572538567</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.76362945411734</v>
+        <v>60.17622553180826</v>
       </c>
       <c r="C6" t="n">
-        <v>125.8669279183708</v>
+        <v>107.9146893985137</v>
       </c>
       <c r="D6" t="n">
-        <v>51.36111289537615</v>
+        <v>48.46299367243955</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.36357511240336</v>
+        <v>47.31042186765379</v>
       </c>
       <c r="C7" t="n">
-        <v>113.9043321421234</v>
+        <v>101.6275771005171</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>41.20198765183014</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.28214680621311</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="C8" t="n">
-        <v>85.78511439708629</v>
+        <v>84.9506288484765</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>56.24530772400399</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>38.29306920414684</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.896670183085952</v>
+        <v>7.907865862625895</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6179636987746</v>
+        <v>105.7677059126214</v>
       </c>
       <c r="D21" t="n">
-        <v>9.87083772885744</v>
+        <v>9.88483232828237</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.069966128908781</v>
+        <v>13.25457575503619</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27300797723862</v>
+        <v>12.92274503100077</v>
       </c>
       <c r="D2" t="n">
-        <v>30.00810032800801</v>
+        <v>23.75633094736432</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.76672926148353</v>
+        <v>30.41945261608742</v>
       </c>
       <c r="C3" t="n">
-        <v>19.88529974951915</v>
+        <v>34.66551143695488</v>
       </c>
       <c r="D3" t="n">
-        <v>89.24086631603507</v>
+        <v>60.64746442984671</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54417563225577</v>
+        <v>46.30314872309656</v>
       </c>
       <c r="C4" t="n">
-        <v>58.6064109527176</v>
+        <v>75.03203179247099</v>
       </c>
       <c r="D4" t="n">
-        <v>121.0161125116873</v>
+        <v>89.22417660506288</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.33282213840224</v>
+        <v>59.07666810305183</v>
       </c>
       <c r="C5" t="n">
-        <v>107.4031988446011</v>
+        <v>109.26851948267</v>
       </c>
       <c r="D5" t="n">
-        <v>93.09422605520381</v>
+        <v>78.46618526192633</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.9623844587317</v>
+        <v>67.34102027740147</v>
       </c>
       <c r="C6" t="n">
-        <v>142.4908617943821</v>
+        <v>130.1336034410275</v>
       </c>
       <c r="D6" t="n">
-        <v>61.62528514327655</v>
+        <v>55.94980166502573</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.46633982617978</v>
+        <v>58.14989827024283</v>
       </c>
       <c r="C7" t="n">
-        <v>144.745936271037</v>
+        <v>125.4025612542621</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>45.27427712904591</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.04424506661589</v>
+        <v>39.47116644924301</v>
       </c>
       <c r="C8" t="n">
-        <v>114.1576230498191</v>
+        <v>108.2327756546896</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.52968609640354</v>
+        <v>20.96718571959912</v>
       </c>
       <c r="C9" t="n">
-        <v>78.65468082114168</v>
+        <v>77.87811838708245</v>
       </c>
       <c r="D9" t="n">
         <v>37.49687181600267</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>50.82016991033614</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
         <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.067569185127303</v>
+        <v>8.081681187059292</v>
       </c>
       <c r="C21" t="n">
-        <v>113.9544147399232</v>
+        <v>114.1537467672125</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09290762955004</v>
+        <v>11.11231163220653</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.39648720379547</v>
+        <v>11.86049401500571</v>
       </c>
       <c r="C2" t="n">
-        <v>6.902668108559324</v>
+        <v>8.580474935117122</v>
       </c>
       <c r="D2" t="n">
-        <v>24.45140832197106</v>
+        <v>19.28054316370311</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.38937829015427</v>
+        <v>34.86676971632547</v>
       </c>
       <c r="C3" t="n">
-        <v>34.53297549688155</v>
+        <v>53.42180132659018</v>
       </c>
       <c r="D3" t="n">
-        <v>97.29610622938014</v>
+        <v>67.05336820005715</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.70037132822225</v>
+        <v>28.38428962518378</v>
       </c>
       <c r="C4" t="n">
-        <v>86.79925977557325</v>
+        <v>97.03496134005049</v>
       </c>
       <c r="D4" t="n">
-        <v>113.1542768960789</v>
+        <v>86.90136153681492</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.64311116620645</v>
+        <v>37.92000507653306</v>
       </c>
       <c r="C5" t="n">
-        <v>85.14206965080464</v>
+        <v>77.7544181763474</v>
       </c>
       <c r="D5" t="n">
-        <v>62.73367830137119</v>
+        <v>55.27239574909544</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>36.10573531908495</v>
       </c>
       <c r="C6" t="n">
-        <v>95.31592110991434</v>
+        <v>82.59639785369266</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>26.17044855210722</v>
       </c>
       <c r="C7" t="n">
-        <v>80.24805734513427</v>
+        <v>76.11588125795946</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>57.91329707351935</v>
+        <v>57.32915718949249</v>
       </c>
       <c r="D8" t="n">
         <v>27.62147165898401</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>38.71718421238145</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
         <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>24.89024954576939</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>18.41660518396592</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.501313223971626</v>
+        <v>6.727917017203391</v>
       </c>
       <c r="C2" t="n">
-        <v>3.53036474447153</v>
+        <v>3.516620276612075</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21298249855933</v>
+        <v>14.24417744091697</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.74280746368311</v>
+        <v>38.93611395042851</v>
       </c>
       <c r="C3" t="n">
-        <v>31.20485077948487</v>
+        <v>43.83012625609885</v>
       </c>
       <c r="D3" t="n">
-        <v>95.08226515630359</v>
+        <v>67.95166734944299</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.39102299039327</v>
+        <v>45.69053815564656</v>
       </c>
       <c r="C4" t="n">
-        <v>89.76021085158163</v>
+        <v>118.8336873651467</v>
       </c>
       <c r="D4" t="n">
-        <v>133.357662901774</v>
+        <v>98.51543687805467</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.03014074585795</v>
+        <v>41.87153958612647</v>
       </c>
       <c r="C5" t="n">
-        <v>121.9821522526662</v>
+        <v>125.0992012136498</v>
       </c>
       <c r="D5" t="n">
-        <v>81.33779729684825</v>
+        <v>70.19496085364696</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.58875518957439</v>
+        <v>43.59254331167113</v>
       </c>
       <c r="C6" t="n">
-        <v>115.8845172615893</v>
+        <v>103.97002712285</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="C7" t="n">
-        <v>104.7416808183879</v>
+        <v>96.05812237432491</v>
       </c>
       <c r="D7" t="n">
         <v>30.78171751895449</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>75.8547363686298</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>44.04218376021615</v>
+        <v>45.48437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>15.70599977254047</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.602433237509047</v>
+        <v>6.367615609744812</v>
       </c>
       <c r="C2" t="n">
-        <v>5.714753386420683</v>
+        <v>6.715154297048183</v>
       </c>
       <c r="D2" t="n">
-        <v>16.39420491321749</v>
+        <v>19.28643364992859</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.90631736193583</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="C3" t="n">
-        <v>21.55917958525995</v>
+        <v>27.22877257728529</v>
       </c>
       <c r="D3" t="n">
-        <v>87.23810099937157</v>
+        <v>63.7448784367454</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.55916388972673</v>
+        <v>60.44424265506763</v>
       </c>
       <c r="C4" t="n">
-        <v>84.36158022592842</v>
+        <v>115.0176340387393</v>
       </c>
       <c r="D4" t="n">
-        <v>148.966469651594</v>
+        <v>109.0191555657913</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>54.3151917374548</v>
       </c>
       <c r="C5" t="n">
-        <v>143.7278639017331</v>
+        <v>172.1249162470721</v>
       </c>
       <c r="D5" t="n">
-        <v>107.4277425372073</v>
+        <v>87.52280783360315</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.50574860306991</v>
+        <v>50.03280825153021</v>
       </c>
       <c r="C6" t="n">
-        <v>154.606610212492</v>
+        <v>150.541192969206</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80388110999145</v>
+        <v>47.73846386670541</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.06307819944583</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="C7" t="n">
-        <v>134.5053259680385</v>
+        <v>121.8692512666778</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="C8" t="n">
-        <v>106.814150222053</v>
+        <v>99.72102305886976</v>
       </c>
       <c r="D8" t="n">
         <v>30.70906818884022</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>66.89530681967339</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
         <v>29.07347651356504</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.713550654538184</v>
+        <v>3.770892932011999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.582978209873358</v>
+        <v>3.079742548222244</v>
       </c>
       <c r="D2" t="n">
-        <v>11.30875180521901</v>
+        <v>13.31838935581223</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.66088043587412</v>
+        <v>29.90894380987908</v>
       </c>
       <c r="C3" t="n">
-        <v>23.30178176029805</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D3" t="n">
-        <v>84.55302102825655</v>
+        <v>65.87527095496098</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.08992954482576</v>
+        <v>66.67245009080939</v>
       </c>
       <c r="C4" t="n">
-        <v>81.71969715380025</v>
+        <v>108.8021893231528</v>
       </c>
       <c r="D4" t="n">
-        <v>159.061781294364</v>
+        <v>116.3704823751914</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.2157731774186</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="C5" t="n">
-        <v>167.8297700409923</v>
+        <v>206.0933868140117</v>
       </c>
       <c r="D5" t="n">
-        <v>117.2206758870692</v>
+        <v>95.20498361933444</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.30699359845555</v>
+        <v>43.39128503230054</v>
       </c>
       <c r="C6" t="n">
-        <v>188.7400143937451</v>
+        <v>185.4796302679414</v>
       </c>
       <c r="D6" t="n">
-        <v>51.07935130425731</v>
+        <v>46.97368240509714</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>141.2725128934118</v>
+        <v>130.0737168310684</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>83.28165775125692</v>
+        <v>80.52785544084462</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
         <v>23.27821981539612</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>12.90016483380309</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.009457624143973</v>
+        <v>4.468915549731481</v>
       </c>
       <c r="C2" t="n">
-        <v>3.002184479586747</v>
+        <v>5.94644584462293</v>
       </c>
       <c r="D2" t="n">
-        <v>16.20767284941059</v>
+        <v>10.80904222375738</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.11891464540088</v>
+        <v>21.622993186036</v>
       </c>
       <c r="C3" t="n">
-        <v>16.33137306014569</v>
+        <v>19.97856578142259</v>
       </c>
       <c r="D3" t="n">
-        <v>75.0595207281899</v>
+        <v>61.54576357923254</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.10796085640069</v>
+        <v>62.85639676440204</v>
       </c>
       <c r="C4" t="n">
-        <v>70.45021525675112</v>
+        <v>89.92612621359933</v>
       </c>
       <c r="D4" t="n">
-        <v>164.141343916137</v>
+        <v>121.7818757209998</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.75130870231863</v>
+        <v>74.58828183015143</v>
       </c>
       <c r="C5" t="n">
-        <v>161.0066234964769</v>
+        <v>205.2098138801896</v>
       </c>
       <c r="D5" t="n">
-        <v>142.6233977344554</v>
+        <v>112.0419567471673</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.25544399621598</v>
+        <v>56.07055663264809</v>
       </c>
       <c r="C6" t="n">
-        <v>226.174054356676</v>
+        <v>253.2231671040841</v>
       </c>
       <c r="D6" t="n">
-        <v>71.20517924131691</v>
+        <v>62.51082157250717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>201.3986692923034</v>
+        <v>189.9004401801648</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>127.0921490532708</v>
+        <v>119.5817791157827</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>58.90780749792134</v>
+        <v>58.13124506386212</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
         <v>25.0542014123786</v>
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.805834938737384</v>
+        <v>3.603995822290041</v>
       </c>
       <c r="C2" t="n">
-        <v>1.91146278016854</v>
+        <v>3.328124717396687</v>
       </c>
       <c r="D2" t="n">
-        <v>11.82515109765283</v>
+        <v>8.47346443535422</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65749322440488</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="C3" t="n">
-        <v>14.29915531235479</v>
+        <v>21.87333885061894</v>
       </c>
       <c r="D3" t="n">
-        <v>71.69212610262333</v>
+        <v>57.29479601984386</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.93905919354124</v>
+        <v>56.0793923619863</v>
       </c>
       <c r="C4" t="n">
-        <v>59.18073335970198</v>
+        <v>74.95545547153972</v>
       </c>
       <c r="D4" t="n">
-        <v>164.8943444052943</v>
+        <v>124.3854706326624</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.2245521534946</v>
+        <v>83.64490440182826</v>
       </c>
       <c r="C5" t="n">
-        <v>154.2816517223863</v>
+        <v>195.0732688338413</v>
       </c>
       <c r="D5" t="n">
-        <v>160.9575361112646</v>
+        <v>124.8537642875881</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.90955000915161</v>
+        <v>67.05925868628265</v>
       </c>
       <c r="C6" t="n">
-        <v>247.6684385934556</v>
+        <v>292.7100415165951</v>
       </c>
       <c r="D6" t="n">
-        <v>85.77627866774809</v>
+        <v>73.45927197026759</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>23.65521093382689</v>
       </c>
       <c r="C7" t="n">
-        <v>249.547503699384</v>
+        <v>246.7328330313084</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>165.0612415150162</v>
+        <v>157.0501802483622</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>70.9999939711293</v>
+        <v>67.56093176315272</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.080143458849744</v>
+        <v>5.746169312956581</v>
       </c>
       <c r="C2" t="n">
-        <v>7.494661974220151</v>
+        <v>8.922123136195014</v>
       </c>
       <c r="D2" t="n">
-        <v>19.03117924682442</v>
+        <v>11.53651727260427</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.12949288596934</v>
+        <v>15.77177686872501</v>
       </c>
       <c r="C3" t="n">
-        <v>10.926851948267</v>
+        <v>17.53892273636927</v>
       </c>
       <c r="D3" t="n">
-        <v>66.0667117572891</v>
+        <v>51.83627878423158</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.56595400819845</v>
+        <v>46.8008948091497</v>
       </c>
       <c r="C4" t="n">
-        <v>48.23031946653305</v>
+        <v>65.57485615746145</v>
       </c>
       <c r="D4" t="n">
-        <v>161.3845963626119</v>
+        <v>124.1429789497134</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.04645490839843</v>
+        <v>83.79216655746528</v>
       </c>
       <c r="C5" t="n">
-        <v>133.9594742444773</v>
+        <v>169.9896149903352</v>
       </c>
       <c r="D5" t="n">
-        <v>178.5308200172825</v>
+        <v>135.211202567392</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.30076862152737</v>
+        <v>84.52847733565039</v>
       </c>
       <c r="C6" t="n">
-        <v>250.0432862900287</v>
+        <v>300.8811276590413</v>
       </c>
       <c r="D6" t="n">
-        <v>108.5989675483737</v>
+        <v>90.12345750215297</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.05173919535137</v>
+        <v>42.87881273068369</v>
       </c>
       <c r="C7" t="n">
-        <v>294.8816674383889</v>
+        <v>321.1718892104142</v>
       </c>
       <c r="D7" t="n">
-        <v>54.73636150257666</v>
+        <v>51.26293812495145</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>231.1524969649115</v>
+        <v>222.8076414788136</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>122.4749896001981</v>
+        <v>115.1531152219253</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.380959166976768</v>
+        <v>8.317366550378978</v>
       </c>
       <c r="C2" t="n">
-        <v>5.542947538177491</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="D2" t="n">
-        <v>7.450483327529043</v>
+        <v>6.536476214875263</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.88731999818987</v>
+        <v>4.114504628498382</v>
       </c>
       <c r="C2" t="n">
-        <v>4.196971435655114</v>
+        <v>5.067781649322035</v>
       </c>
       <c r="D2" t="n">
-        <v>14.00659449648924</v>
+        <v>8.490154146326416</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24792450528471</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2212373908208</v>
+        <v>25.33399950808894</v>
       </c>
       <c r="D3" t="n">
-        <v>73.68507394224436</v>
+        <v>56.66156875060466</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.91575929054657</v>
+        <v>64.17095694038852</v>
       </c>
       <c r="C4" t="n">
-        <v>70.29706261488862</v>
+        <v>94.91634979428588</v>
       </c>
       <c r="D4" t="n">
-        <v>165.4686668122787</v>
+        <v>127.0273537047906</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.20256848890689</v>
+        <v>49.94641445355649</v>
       </c>
       <c r="C5" t="n">
-        <v>206.7560665143783</v>
+        <v>254.7880729446535</v>
       </c>
       <c r="D5" t="n">
-        <v>162.7001382863027</v>
+        <v>125.5655313731671</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.37992066601029</v>
+        <v>26.60634453279281</v>
       </c>
       <c r="C6" t="n">
-        <v>245.6558557997497</v>
+        <v>270.4911274740813</v>
       </c>
       <c r="D6" t="n">
-        <v>84.20646408865744</v>
+        <v>73.49952362614172</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>162.5322594288764</v>
+        <v>156.663371652889</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>90.20788780471817</v>
+        <v>84.86718029361552</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>25.45180923259856</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.990624491314037</v>
+        <v>7.148105034621026</v>
       </c>
       <c r="C2" t="n">
-        <v>3.872994693253667</v>
+        <v>4.966661635784614</v>
       </c>
       <c r="D2" t="n">
-        <v>9.078221021170256</v>
+        <v>12.13145638137784</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.43245201595411</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="C3" t="n">
-        <v>14.18625432636641</v>
+        <v>13.57757074973339</v>
       </c>
       <c r="D3" t="n">
-        <v>9.395325529641976</v>
+        <v>8.62465358180823</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3988483414613</v>
+        <v>13.39852691876104</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14691190529739</v>
+        <v>70.14522916292543</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576335098995447</v>
+        <v>1.576297284560122</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.859070298944964</v>
+        <v>4.91855599827652</v>
       </c>
       <c r="C2" t="n">
-        <v>4.658392856651115</v>
+        <v>3.235840433197487</v>
       </c>
       <c r="D2" t="n">
-        <v>19.88039101099791</v>
+        <v>10.70988570562845</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98914402199105</v>
+        <v>21.95187866695868</v>
       </c>
       <c r="C3" t="n">
-        <v>14.7753029489145</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D3" t="n">
-        <v>14.75075925630833</v>
+        <v>16.72898088036565</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.33704256219292</v>
+        <v>20.36930136771282</v>
       </c>
       <c r="C4" t="n">
-        <v>22.50067563363265</v>
+        <v>21.22440361811179</v>
       </c>
       <c r="D4" t="n">
-        <v>19.99918248321178</v>
+        <v>19.5907754382451</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44491676973904</v>
+        <v>15.44260881576919</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16637776801782</v>
+        <v>86.15350181429125</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251561425208219</v>
+        <v>3.251075540161934</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.451645001682538</v>
+        <v>5.279839153439347</v>
       </c>
       <c r="C2" t="n">
-        <v>5.568472978487908</v>
+        <v>4.424736903040374</v>
       </c>
       <c r="D2" t="n">
-        <v>21.79676252968769</v>
+        <v>13.32231634662922</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.86428213710246</v>
+        <v>19.17844140246144</v>
       </c>
       <c r="C3" t="n">
-        <v>16.80752069670539</v>
+        <v>14.40223882130071</v>
       </c>
       <c r="D3" t="n">
-        <v>27.22877257728529</v>
+        <v>21.41191742962294</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.33850733598268</v>
+        <v>32.85124167950677</v>
       </c>
       <c r="C4" t="n">
-        <v>30.82196917482861</v>
+        <v>34.089225534562</v>
       </c>
       <c r="D4" t="n">
-        <v>22.90908267859932</v>
+        <v>23.57274412667016</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.00186568441726</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="C5" t="n">
-        <v>26.35992585902687</v>
+        <v>24.59277999138261</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>29.50151851261666</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
         <v>12.19625172985813</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
@@ -5294,7 +5294,7 @@
         <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74301881252666</v>
+        <v>16.74000597551683</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1324147564126</v>
+        <v>102.1140364506526</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022905643757999</v>
+        <v>5.022001792655048</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.027529993447916</v>
+        <v>6.712209053935443</v>
       </c>
       <c r="C2" t="n">
-        <v>6.734789251133119</v>
+        <v>4.207770660401829</v>
       </c>
       <c r="D2" t="n">
-        <v>24.1460847859503</v>
+        <v>25.29178435680633</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>18.58448404139212</v>
       </c>
       <c r="C3" t="n">
-        <v>19.63004534641497</v>
+        <v>16.03194001035041</v>
       </c>
       <c r="D3" t="n">
-        <v>37.7383817512474</v>
+        <v>26.77225989481052</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.83473189498382</v>
+        <v>35.07195498651306</v>
       </c>
       <c r="C4" t="n">
-        <v>37.21609197258809</v>
+        <v>35.21234490822035</v>
       </c>
       <c r="D4" t="n">
-        <v>30.71986741358695</v>
+        <v>28.47362866627024</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.54369260617026</v>
+        <v>33.82120841130262</v>
       </c>
       <c r="C5" t="n">
-        <v>43.17235529425349</v>
+        <v>45.70035563268903</v>
       </c>
       <c r="D5" t="n">
-        <v>31.3668391506856</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>14.81260936167588</v>
       </c>
       <c r="C6" t="n">
-        <v>27.69313924139403</v>
+        <v>26.24407962992574</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.46575898910303</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.29864089520282</v>
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07608686019915</v>
+        <v>18.07340617763613</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9249476117754</v>
+        <v>117.9074593493405</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886128327694913</v>
+        <v>6.885107115289956</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.043638867343365</v>
+        <v>6.826091787628073</v>
       </c>
       <c r="C2" t="n">
-        <v>8.514697838932587</v>
+        <v>8.194648087348126</v>
       </c>
       <c r="D2" t="n">
-        <v>32.9965403397353</v>
+        <v>25.01689499961722</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.98776136365931</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0549621759046</v>
+        <v>15.25635932399543</v>
       </c>
       <c r="D3" t="n">
-        <v>44.87077882260047</v>
+        <v>37.65984193490765</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.87454158250144</v>
+        <v>26.06147455693583</v>
       </c>
       <c r="C4" t="n">
-        <v>36.87149852839745</v>
+        <v>31.8557495074005</v>
       </c>
       <c r="D4" t="n">
-        <v>36.46309148343079</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.74571164906685</v>
+        <v>26.5808190924824</v>
       </c>
       <c r="C5" t="n">
-        <v>42.21515128261285</v>
+        <v>41.55247158224626</v>
       </c>
       <c r="D5" t="n">
-        <v>28.74066404182538</v>
+        <v>28.17615911188346</v>
       </c>
     </row>
     <row r="6">
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.19625172985813</v>
+        <v>16.70443718775948</v>
       </c>
       <c r="C6" t="n">
-        <v>33.56988099901544</v>
+        <v>34.5359207399943</v>
       </c>
       <c r="D6" t="n">
         <v>30.47050349670826</v>
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>19.94224111636546</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
         <v>31.14103717870882</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068191723897331</v>
+        <v>7.067266589657689</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14782137702464</v>
+        <v>67.13903260174804</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301143792922998</v>
+        <v>5.300449942243267</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.587707021945345</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C2" t="n">
-        <v>4.658392856651115</v>
+        <v>6.961572970814132</v>
       </c>
       <c r="D2" t="n">
-        <v>31.55926170071797</v>
+        <v>21.61808444751477</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.31588608105599</v>
+        <v>22.14331946928681</v>
       </c>
       <c r="C3" t="n">
-        <v>29.41806995775567</v>
+        <v>26.42864819832414</v>
       </c>
       <c r="D3" t="n">
-        <v>62.63550353094651</v>
+        <v>50.21148633370311</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.29044275620359</v>
+        <v>33.24688600431823</v>
       </c>
       <c r="C4" t="n">
-        <v>48.67701467196535</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="D4" t="n">
-        <v>52.28886447588937</v>
+        <v>43.71231653158923</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.21957699504858</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="C5" t="n">
-        <v>57.99674562838034</v>
+        <v>52.59713325502288</v>
       </c>
       <c r="D5" t="n">
-        <v>36.20194659410114</v>
+        <v>33.13398501832986</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.21891404251382</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>54.017722183068</v>
+        <v>53.7762122478233</v>
       </c>
       <c r="D6" t="n">
-        <v>32.92585450502953</v>
+        <v>33.16736444027425</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.78845088416398</v>
       </c>
       <c r="D7" t="n">
         <v>33.59638818703009</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>23.61594102565702</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>33.41280136633594</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6241,7 +6241,7 @@
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.294809747183997</v>
+        <v>7.295703441544018</v>
       </c>
       <c r="C21" t="n">
-        <v>77.50735356382997</v>
+        <v>77.5168490664052</v>
       </c>
       <c r="D21" t="n">
-        <v>6.382958528785998</v>
+        <v>6.383740511351016</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.6018524004323</v>
+        <v>6.800566347317655</v>
       </c>
       <c r="C2" t="n">
-        <v>6.958627727701391</v>
+        <v>8.083710596768237</v>
       </c>
       <c r="D2" t="n">
-        <v>32.13162061229386</v>
+        <v>16.04862972132261</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.40147805777471</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="C3" t="n">
-        <v>22.47220495020949</v>
+        <v>26.88025214227767</v>
       </c>
       <c r="D3" t="n">
-        <v>73.35127972280044</v>
+        <v>56.23941723777853</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.37000537797658</v>
+        <v>39.46233071990478</v>
       </c>
       <c r="C4" t="n">
-        <v>63.67321085433538</v>
+        <v>54.42023874180919</v>
       </c>
       <c r="D4" t="n">
-        <v>71.42018198854697</v>
+        <v>59.88268296823845</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.31270415823178</v>
+        <v>43.44233591292137</v>
       </c>
       <c r="C5" t="n">
-        <v>76.60086462385739</v>
+        <v>60.96653243372694</v>
       </c>
       <c r="D5" t="n">
-        <v>47.44295780772712</v>
+        <v>41.89608327873264</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.48937768726721</v>
+        <v>38.52083467153211</v>
       </c>
       <c r="C6" t="n">
-        <v>74.94858323761002</v>
+        <v>70.88316599432396</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>25.3919226226395</v>
       </c>
       <c r="C7" t="n">
-        <v>60.42558944868693</v>
+        <v>60.12615639889166</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.7201294554942</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.50946312279659</v>
+        <v>7.513145251554567</v>
       </c>
       <c r="C21" t="n">
-        <v>87.29750880251035</v>
+        <v>87.34031354932183</v>
       </c>
       <c r="D21" t="n">
-        <v>7.50946312279659</v>
+        <v>7.513145251554567</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_72_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_72_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631308466</v>
+        <v>10.84497613009552</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907187525007</v>
+        <v>37.78907123762858</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.233337158441252</v>
+        <v>1.547234381892973</v>
       </c>
       <c r="C2" t="n">
-        <v>9.558295648546945</v>
+        <v>4.034001316750144</v>
       </c>
       <c r="D2" t="n">
-        <v>15.11204241147115</v>
+        <v>12.20017872067511</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.70782439922873</v>
+        <v>14.88329519638165</v>
       </c>
       <c r="C3" t="n">
-        <v>29.52606220522282</v>
+        <v>42.05807164993336</v>
       </c>
       <c r="D3" t="n">
-        <v>55.92525797241955</v>
+        <v>63.52889394181111</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.03214529899544</v>
+        <v>27.04420400888689</v>
       </c>
       <c r="C4" t="n">
-        <v>61.74604011089889</v>
+        <v>135.9357323731261</v>
       </c>
       <c r="D4" t="n">
-        <v>73.23248825058657</v>
+        <v>74.72572650874598</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.20443417332415</v>
+        <v>26.11448893296516</v>
       </c>
       <c r="C5" t="n">
-        <v>82.76133146800613</v>
+        <v>159.9021573291993</v>
       </c>
       <c r="D5" t="n">
-        <v>53.97158004096841</v>
+        <v>46.75573441475435</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.22777513404782</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="C6" t="n">
-        <v>84.89074223851746</v>
+        <v>108.2769543013807</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33845058272045</v>
+        <v>29.38370878810704</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.59071868498287</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>82.16442886382406</v>
+        <v>51.74203100462389</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>29.22466566001905</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.77730750205199</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>60.75054793879262</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.717776224367244</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.47220280459055</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.682498252413149</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.29853341754904</v>
+        <v>1.764200624531518</v>
       </c>
       <c r="C2" t="n">
-        <v>9.351146882950868</v>
+        <v>10.43008760991811</v>
       </c>
       <c r="D2" t="n">
-        <v>25.58434517267188</v>
+        <v>12.44070690821558</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.27785996249763</v>
+        <v>9.881290643244148</v>
       </c>
       <c r="C3" t="n">
-        <v>33.48250545333747</v>
+        <v>27.44475707221959</v>
       </c>
       <c r="D3" t="n">
-        <v>54.90424036000287</v>
+        <v>59.27792638242241</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.90001026954963</v>
+        <v>28.09074706161399</v>
       </c>
       <c r="C4" t="n">
-        <v>67.36163697919065</v>
+        <v>119.3186707310446</v>
       </c>
       <c r="D4" t="n">
-        <v>83.46818981506382</v>
+        <v>88.07553179109411</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.69592992025331</v>
+        <v>33.10944132572369</v>
       </c>
       <c r="C5" t="n">
-        <v>98.6411005841983</v>
+        <v>208.7686493080843</v>
       </c>
       <c r="D5" t="n">
-        <v>65.97344572538567</v>
+        <v>61.13833828197013</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.17622553180826</v>
+        <v>24.99627829782805</v>
       </c>
       <c r="C6" t="n">
-        <v>107.9146893985137</v>
+        <v>180.6494315630471</v>
       </c>
       <c r="D6" t="n">
-        <v>48.46299367243955</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.31042186765379</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6275771005171</v>
+        <v>101.507803880599</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.37389131106456</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>84.9506288484765</v>
+        <v>47.89947049020188</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.72012945549421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.27040689149115</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.907865862625895</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7677059126214</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.88483232828237</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>13.25457575503619</v>
+        <v>0.9660397409788614</v>
       </c>
       <c r="C2" t="n">
-        <v>12.92274503100077</v>
+        <v>4.602433237509047</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75633094736432</v>
+        <v>8.580474935117122</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.41945261608742</v>
+        <v>9.326603190344699</v>
       </c>
       <c r="C3" t="n">
-        <v>34.66551143695488</v>
+        <v>35.37236978401258</v>
       </c>
       <c r="D3" t="n">
-        <v>60.64746442984671</v>
+        <v>58.17836895366599</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.30314872309656</v>
+        <v>30.29869764846506</v>
       </c>
       <c r="C4" t="n">
-        <v>75.03203179247099</v>
+        <v>111.2526315929528</v>
       </c>
       <c r="D4" t="n">
-        <v>89.22417660506288</v>
+        <v>95.96289284701298</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.07666810305183</v>
+        <v>32.66765485881262</v>
       </c>
       <c r="C5" t="n">
-        <v>109.26851948267</v>
+        <v>242.6880324898116</v>
       </c>
       <c r="D5" t="n">
-        <v>78.46618526192633</v>
+        <v>67.34789251133121</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.34102027740147</v>
+        <v>17.87173520810894</v>
       </c>
       <c r="C6" t="n">
-        <v>130.1336034410275</v>
+        <v>218.0432198701039</v>
       </c>
       <c r="D6" t="n">
-        <v>55.94980166502573</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.14989827024283</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>125.4025612542621</v>
+        <v>92.16549272698632</v>
       </c>
       <c r="D7" t="n">
-        <v>45.27427712904591</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.47116644924301</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>108.2327756546896</v>
+        <v>40.63944621729671</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.96718571959912</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>77.87811838708245</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>50.82016991033614</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.863979037466197</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.081681187059292</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.1537467672125</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11231163220653</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.86049401500571</v>
+        <v>0.7804894248762142</v>
       </c>
       <c r="C2" t="n">
-        <v>8.580474935117122</v>
+        <v>6.859471209572464</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28054316370311</v>
+        <v>11.79766216193392</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34.86676971632547</v>
+        <v>6.34699890795563</v>
       </c>
       <c r="C3" t="n">
-        <v>53.42180132659018</v>
+        <v>26.05558407071035</v>
       </c>
       <c r="D3" t="n">
-        <v>67.05336820005715</v>
+        <v>52.53331965424683</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>24.46613453753476</v>
       </c>
       <c r="C4" t="n">
-        <v>97.03496134005049</v>
+        <v>100.3787940207151</v>
       </c>
       <c r="D4" t="n">
-        <v>86.90136153681492</v>
+        <v>102.0634730812026</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.92000507653306</v>
+        <v>39.07355862902306</v>
       </c>
       <c r="C5" t="n">
-        <v>77.7544181763474</v>
+        <v>226.4401079845269</v>
       </c>
       <c r="D5" t="n">
-        <v>55.27239574909544</v>
+        <v>83.30129270534188</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>28.05540414426111</v>
       </c>
       <c r="C6" t="n">
-        <v>82.59639785369266</v>
+        <v>299.6735779828177</v>
       </c>
       <c r="D6" t="n">
-        <v>29.78622534684823</v>
+        <v>47.2956956520901</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>76.11588125795946</v>
+        <v>188.5829347610656</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>57.32915718949249</v>
+        <v>75.35404503946393</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>38.71718421238145</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.727917017203391</v>
+        <v>0.5753041546886308</v>
       </c>
       <c r="C2" t="n">
-        <v>3.516620276612075</v>
+        <v>4.197953183359361</v>
       </c>
       <c r="D2" t="n">
-        <v>14.24417744091697</v>
+        <v>9.806677817721388</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38.93611395042851</v>
+        <v>4.830198704894308</v>
       </c>
       <c r="C3" t="n">
-        <v>43.83012625609885</v>
+        <v>26.64954143177967</v>
       </c>
       <c r="D3" t="n">
-        <v>67.95166734944299</v>
+        <v>50.91834468076082</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.69053815564656</v>
+        <v>20.3310132072472</v>
       </c>
       <c r="C4" t="n">
-        <v>118.8336873651467</v>
+        <v>87.08003961898784</v>
       </c>
       <c r="D4" t="n">
-        <v>98.51543687805467</v>
+        <v>104.5777289517787</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.87153958612647</v>
+        <v>40.66889864842413</v>
       </c>
       <c r="C5" t="n">
-        <v>125.0992012136498</v>
+        <v>217.5798349536994</v>
       </c>
       <c r="D5" t="n">
-        <v>70.19496085364696</v>
+        <v>94.56684761157402</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.59254331167113</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="C6" t="n">
-        <v>103.97002712285</v>
+        <v>335.5780550225321</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>56.67433147075987</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.79305652304895</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>96.05812237432491</v>
+        <v>269.4897448157495</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>116.4941825859265</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48437113775471</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.367615609744812</v>
+        <v>1.743583922742335</v>
       </c>
       <c r="C2" t="n">
-        <v>6.715154297048183</v>
+        <v>11.91547188644354</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28643364992859</v>
+        <v>10.66865230205009</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.7483380970101</v>
+        <v>3.445934441906305</v>
       </c>
       <c r="C3" t="n">
-        <v>27.22877257728529</v>
+        <v>21.70644174089698</v>
       </c>
       <c r="D3" t="n">
-        <v>63.7448784367454</v>
+        <v>47.33496556025997</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.44424265506763</v>
+        <v>15.31526418625024</v>
       </c>
       <c r="C4" t="n">
-        <v>115.0176340387393</v>
+        <v>77.40589774133977</v>
       </c>
       <c r="D4" t="n">
-        <v>109.0191555657913</v>
+        <v>105.6625601649715</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.3151917374548</v>
+        <v>36.81553890925539</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1249162470721</v>
+        <v>191.8825887950391</v>
       </c>
       <c r="D5" t="n">
-        <v>87.52280783360315</v>
+        <v>107.0104997629024</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.03280825153021</v>
+        <v>42.38499363544755</v>
       </c>
       <c r="C6" t="n">
-        <v>150.541192969206</v>
+        <v>341.1730351890346</v>
       </c>
       <c r="D6" t="n">
-        <v>47.73846386670541</v>
+        <v>69.15234479173684</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>121.8692512666778</v>
+        <v>362.0744438124491</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.7745421853885</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>99.72102305886976</v>
+        <v>211.4586380177205</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>81.09530561389926</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>20.28094407433061</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.90078672860884</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.770892932011999</v>
+        <v>1.227184630308513</v>
       </c>
       <c r="C2" t="n">
-        <v>3.079742548222244</v>
+        <v>6.671957398061323</v>
       </c>
       <c r="D2" t="n">
-        <v>13.31838935581223</v>
+        <v>7.852999886270236</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.90894380987908</v>
+        <v>5.576326960121883</v>
       </c>
       <c r="C3" t="n">
-        <v>28.53940576245478</v>
+        <v>32.63329368916398</v>
       </c>
       <c r="D3" t="n">
-        <v>65.87527095496098</v>
+        <v>51.19323403794993</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66.67245009080939</v>
+        <v>25.32123678793373</v>
       </c>
       <c r="C4" t="n">
-        <v>108.8021893231528</v>
+        <v>110.4996311037955</v>
       </c>
       <c r="D4" t="n">
-        <v>116.3704823751914</v>
+        <v>108.1640533153923</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.13142499031139</v>
+        <v>25.23091599914303</v>
       </c>
       <c r="C5" t="n">
-        <v>206.0933868140117</v>
+        <v>288.1429511964389</v>
       </c>
       <c r="D5" t="n">
-        <v>95.20498361933444</v>
+        <v>98.7147316620168</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.39128503230054</v>
+        <v>13.04153650321463</v>
       </c>
       <c r="C6" t="n">
-        <v>185.4796302679414</v>
+        <v>308.6899488986204</v>
       </c>
       <c r="D6" t="n">
-        <v>46.97368240509714</v>
+        <v>58.6064109527176</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.73777555197486</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>130.0737168310684</v>
+        <v>148.6984525283346</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>80.52785544084462</v>
+        <v>59.74916528046088</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.65044106402591</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.78864650614645</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.468915549731481</v>
+        <v>0.6430447462816608</v>
       </c>
       <c r="C2" t="n">
-        <v>5.94644584462293</v>
+        <v>3.856304982281471</v>
       </c>
       <c r="D2" t="n">
-        <v>10.80904222375738</v>
+        <v>6.246860642122455</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.622993186036</v>
+        <v>4.908738521234052</v>
       </c>
       <c r="C3" t="n">
-        <v>19.97856578142259</v>
+        <v>29.16772429317274</v>
       </c>
       <c r="D3" t="n">
-        <v>61.54576357923254</v>
+        <v>45.97524498987813</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62.85639676440204</v>
+        <v>17.17862132891069</v>
       </c>
       <c r="C4" t="n">
-        <v>89.92612621359933</v>
+        <v>92.91260272991813</v>
       </c>
       <c r="D4" t="n">
-        <v>121.7818757209998</v>
+        <v>104.3990508696058</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.58828183015143</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="C5" t="n">
-        <v>205.2098138801896</v>
+        <v>223.2494279457247</v>
       </c>
       <c r="D5" t="n">
-        <v>112.0419567471673</v>
+        <v>102.052673856456</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.07055663264809</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>253.2231671040841</v>
+        <v>309.6559886395993</v>
       </c>
       <c r="D6" t="n">
-        <v>62.51082157250717</v>
+        <v>60.65924540229769</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9004401801648</v>
+        <v>194.3919359270939</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>119.5817791157827</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>28.39999758845172</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.603995822290041</v>
+        <v>1.217367153266045</v>
       </c>
       <c r="C2" t="n">
-        <v>3.328124717396687</v>
+        <v>7.501534208149878</v>
       </c>
       <c r="D2" t="n">
-        <v>8.47346443535422</v>
+        <v>11.00539176460674</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1440802328128</v>
+        <v>3.480295611554943</v>
       </c>
       <c r="C3" t="n">
-        <v>21.87333885061894</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="D3" t="n">
-        <v>57.29479601984386</v>
+        <v>40.49709280018093</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.0793923619863</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C4" t="n">
-        <v>74.95545547153972</v>
+        <v>81.96218883674922</v>
       </c>
       <c r="D4" t="n">
-        <v>124.3854706326624</v>
+        <v>103.9778811044839</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.64490440182826</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="C5" t="n">
-        <v>195.0732688338413</v>
+        <v>198.067599331794</v>
       </c>
       <c r="D5" t="n">
-        <v>124.8537642875881</v>
+        <v>115.9934912567607</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.05925868628265</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>292.7100415165951</v>
+        <v>333.5252205729519</v>
       </c>
       <c r="D6" t="n">
-        <v>73.45927197026759</v>
+        <v>77.24292762243481</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.65521093382689</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>246.7328330313084</v>
+        <v>321.4713222602095</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>157.0501802483622</v>
+        <v>159.8039825587745</v>
       </c>
       <c r="D8" t="n">
-        <v>35.46563581591602</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>67.56093176315272</v>
+        <v>55.80155776168444</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.746169312956581</v>
+        <v>1.550179625005713</v>
       </c>
       <c r="C2" t="n">
-        <v>8.922123136195014</v>
+        <v>18.43034965182537</v>
       </c>
       <c r="D2" t="n">
-        <v>11.53651727260427</v>
+        <v>13.42932684639212</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.77177686872501</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C3" t="n">
-        <v>17.53892273636927</v>
+        <v>25.12292375167588</v>
       </c>
       <c r="D3" t="n">
-        <v>51.83627878423158</v>
+        <v>39.75096454495336</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.8008948091497</v>
+        <v>9.916633560597031</v>
       </c>
       <c r="C4" t="n">
-        <v>65.57485615746145</v>
+        <v>67.22124705748335</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1429789497134</v>
+        <v>101.0296927486308</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.79216655746528</v>
+        <v>23.29196428325558</v>
       </c>
       <c r="C5" t="n">
-        <v>169.9896149903352</v>
+        <v>175.291052593268</v>
       </c>
       <c r="D5" t="n">
-        <v>135.211202567392</v>
+        <v>124.2401719724339</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.52847733565039</v>
+        <v>27.89439752076462</v>
       </c>
       <c r="C6" t="n">
-        <v>300.8811276590413</v>
+        <v>326.4811807949811</v>
       </c>
       <c r="D6" t="n">
-        <v>90.12345750215297</v>
+        <v>93.5448482514531</v>
       </c>
     </row>
     <row r="7">
@@ -3649,10 +3649,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.87881273068369</v>
+        <v>16.40893112878119</v>
       </c>
       <c r="C7" t="n">
-        <v>321.1718892104142</v>
+        <v>393.5149140409533</v>
       </c>
       <c r="D7" t="n">
         <v>51.26293812495145</v>
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>222.8076414788136</v>
+        <v>281.1381813266378</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>115.1531152219253</v>
+        <v>118.7031149204818</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.317366550378978</v>
+        <v>8.839656329038281</v>
       </c>
       <c r="C2" t="n">
-        <v>5.389794896314989</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="D2" t="n">
-        <v>6.536476214875263</v>
+        <v>12.06371578978481</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.114504628498382</v>
+        <v>1.136863841517807</v>
       </c>
       <c r="C2" t="n">
-        <v>5.067781649322035</v>
+        <v>22.2061513223586</v>
       </c>
       <c r="D2" t="n">
-        <v>8.490154146326416</v>
+        <v>14.33547997741192</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.6377194015997</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C3" t="n">
-        <v>25.33399950808894</v>
+        <v>45.94088382022949</v>
       </c>
       <c r="D3" t="n">
-        <v>56.66156875060466</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64.17095694038852</v>
+        <v>8.551022503989717</v>
       </c>
       <c r="C4" t="n">
-        <v>94.91634979428588</v>
+        <v>64.36239774271664</v>
       </c>
       <c r="D4" t="n">
-        <v>127.0273537047906</v>
+        <v>97.31574118346508</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.94641445355649</v>
+        <v>19.88039101099791</v>
       </c>
       <c r="C5" t="n">
-        <v>254.7880729446535</v>
+        <v>152.6372243177729</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5655313731671</v>
+        <v>130.5479009722196</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>270.4911274740813</v>
+        <v>305.1075515258238</v>
       </c>
       <c r="D6" t="n">
-        <v>73.49952362614172</v>
+        <v>107.1096562810313</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="C7" t="n">
-        <v>156.663371652889</v>
+        <v>429.5067666263456</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>61.38377520803181</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>84.86718029361552</v>
+        <v>377.7716078556514</v>
       </c>
       <c r="D8" t="n">
-        <v>25.45180923259856</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>211.1140445735298</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>79.57556016772523</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>9.626036240139976</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.148105034621026</v>
+        <v>7.173630474931444</v>
       </c>
       <c r="C2" t="n">
-        <v>4.966661635784614</v>
+        <v>15.36827856227957</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13145638137784</v>
+        <v>18.17705874412969</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65673246087889</v>
+        <v>14.23043297305752</v>
       </c>
       <c r="C3" t="n">
-        <v>13.57757074973339</v>
+        <v>29.56042337487146</v>
       </c>
       <c r="D3" t="n">
-        <v>8.62465358180823</v>
+        <v>11.24591995214721</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39852691876104</v>
+        <v>11.67668158558485</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14522916292543</v>
+        <v>59.94029880600224</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576297284560122</v>
+        <v>0.7784454390389901</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.91855599827652</v>
+        <v>4.34914232981337</v>
       </c>
       <c r="C2" t="n">
-        <v>3.235840433197487</v>
+        <v>6.957645979997145</v>
       </c>
       <c r="D2" t="n">
-        <v>10.70988570562845</v>
+        <v>20.13760890951058</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.95187866695868</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="C3" t="n">
-        <v>17.20021977840412</v>
+        <v>49.55862411037899</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72898088036565</v>
+        <v>24.41606540461818</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.36930136771282</v>
+        <v>17.07651956766902</v>
       </c>
       <c r="C4" t="n">
-        <v>21.22440361811179</v>
+        <v>47.83467514172159</v>
       </c>
       <c r="D4" t="n">
-        <v>19.5907754382451</v>
+        <v>20.16509784522949</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44260881576919</v>
+        <v>13.62259694608916</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15350181429125</v>
+        <v>73.72228935530603</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251075540161934</v>
+        <v>1.602658464245783</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.279839153439347</v>
+        <v>3.87495818866216</v>
       </c>
       <c r="C2" t="n">
-        <v>4.424736903040374</v>
+        <v>6.621888265144736</v>
       </c>
       <c r="D2" t="n">
-        <v>13.32231634662922</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17844140246144</v>
+        <v>17.59782759862408</v>
       </c>
       <c r="C3" t="n">
-        <v>14.40223882130071</v>
+        <v>35.52944941669207</v>
       </c>
       <c r="D3" t="n">
-        <v>21.41191742962294</v>
+        <v>35.43127464626738</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.85124167950677</v>
+        <v>31.03893541746715</v>
       </c>
       <c r="C4" t="n">
-        <v>34.089225534562</v>
+        <v>94.27821378652546</v>
       </c>
       <c r="D4" t="n">
-        <v>23.57274412667016</v>
+        <v>28.28218786394211</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.54874021341174</v>
+        <v>14.89802141194535</v>
       </c>
       <c r="C5" t="n">
-        <v>24.59277999138261</v>
+        <v>54.21701696703012</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>27.43984833369836</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74000597551683</v>
+        <v>14.82249628290838</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1140364506526</v>
+        <v>87.28803366601599</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022001792655048</v>
+        <v>2.470416047151396</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.712209053935443</v>
+        <v>3.819980317224339</v>
       </c>
       <c r="C2" t="n">
-        <v>4.207770660401829</v>
+        <v>8.458738219790517</v>
       </c>
       <c r="D2" t="n">
-        <v>25.29178435680633</v>
+        <v>24.38661297349077</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.58448404139212</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="C3" t="n">
-        <v>16.03194001035041</v>
+        <v>29.76168165424206</v>
       </c>
       <c r="D3" t="n">
-        <v>26.77225989481052</v>
+        <v>46.70173829102077</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.07195498651306</v>
+        <v>32.99163160121406</v>
       </c>
       <c r="C4" t="n">
-        <v>35.21234490822035</v>
+        <v>91.26621182989624</v>
       </c>
       <c r="D4" t="n">
-        <v>28.47362866627024</v>
+        <v>38.78590655167874</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.82120841130262</v>
+        <v>31.09685853201772</v>
       </c>
       <c r="C5" t="n">
-        <v>45.70035563268903</v>
+        <v>119.65050145508</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>31.51410130632262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.81260936167588</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="C6" t="n">
-        <v>26.24407962992574</v>
+        <v>51.07935130425731</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.40887437551896</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07340617763613</v>
+        <v>16.04642878610114</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9074593493405</v>
+        <v>100.5013171340019</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885107115289956</v>
+        <v>3.378195533916029</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.826091787628073</v>
+        <v>3.334996951326415</v>
       </c>
       <c r="C2" t="n">
-        <v>8.194648087348126</v>
+        <v>12.08335074386974</v>
       </c>
       <c r="D2" t="n">
-        <v>25.01689499961722</v>
+        <v>25.3310542649762</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.88882582970863</v>
+        <v>14.1420756796753</v>
       </c>
       <c r="C3" t="n">
-        <v>15.25635932399543</v>
+        <v>31.35702167364312</v>
       </c>
       <c r="D3" t="n">
-        <v>37.65984193490765</v>
+        <v>54.32010047597602</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.06147455693583</v>
+        <v>30.86025733529424</v>
       </c>
       <c r="C4" t="n">
-        <v>31.8557495074005</v>
+        <v>81.42615459023045</v>
       </c>
       <c r="D4" t="n">
-        <v>30.37527396939631</v>
+        <v>51.51033854642165</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.5808190924824</v>
+        <v>40.17802479630072</v>
       </c>
       <c r="C5" t="n">
-        <v>41.55247158224626</v>
+        <v>145.0286796098601</v>
       </c>
       <c r="D5" t="n">
-        <v>28.17615911188346</v>
+        <v>37.99363615435157</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.70443718775948</v>
+        <v>26.12332466230338</v>
       </c>
       <c r="C6" t="n">
-        <v>34.5359207399943</v>
+        <v>120.19144444012</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>19.22360179685679</v>
+        <v>44.91495746929157</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.067266589657689</v>
+        <v>17.28820086923991</v>
       </c>
       <c r="C21" t="n">
-        <v>67.13903260174804</v>
+        <v>113.2377156935214</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300449942243267</v>
+        <v>4.322050217309978</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.243915399009714</v>
+        <v>3.294745295452295</v>
       </c>
       <c r="C2" t="n">
-        <v>6.961572970814132</v>
+        <v>10.86205659978671</v>
       </c>
       <c r="D2" t="n">
-        <v>21.61808444751477</v>
+        <v>20.04925161612836</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.14331946928681</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="C3" t="n">
-        <v>26.42864819832414</v>
+        <v>39.03428872085318</v>
       </c>
       <c r="D3" t="n">
-        <v>50.21148633370311</v>
+        <v>60.50511101273093</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.24688600431823</v>
+        <v>28.61401858797754</v>
       </c>
       <c r="C4" t="n">
-        <v>36.05468443846411</v>
+        <v>78.98847504058561</v>
       </c>
       <c r="D4" t="n">
-        <v>43.71231653158923</v>
+        <v>64.57936398535519</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.23845118560752</v>
+        <v>43.22144267946583</v>
       </c>
       <c r="C5" t="n">
-        <v>52.59713325502288</v>
+        <v>147.3357867148401</v>
       </c>
       <c r="D5" t="n">
-        <v>33.13398501832986</v>
+        <v>45.84761778832605</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>38.31957639216151</v>
       </c>
       <c r="C6" t="n">
-        <v>53.7762122478233</v>
+        <v>169.7814844770349</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>39.44662275663685</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>37.78845088416398</v>
+        <v>103.9032682789612</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11524969649115</v>
+        <v>40.88979188187965</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>38.93905919354123</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295703441544018</v>
+        <v>17.65754052215594</v>
       </c>
       <c r="C21" t="n">
-        <v>77.5168490664052</v>
+        <v>125.3685377073072</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383740511351016</v>
+        <v>5.297262156646783</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.800566347317655</v>
+        <v>3.107231483941155</v>
       </c>
       <c r="C2" t="n">
-        <v>8.083710596768237</v>
+        <v>7.038149291745383</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04862972132261</v>
+        <v>16.22730780349553</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.98133109808609</v>
+        <v>17.7303635386974</v>
       </c>
       <c r="C3" t="n">
-        <v>26.88025214227767</v>
+        <v>57.0984464789945</v>
       </c>
       <c r="D3" t="n">
-        <v>56.23941723777853</v>
+        <v>64.29465715112362</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.46233071990478</v>
+        <v>20.76494569252429</v>
       </c>
       <c r="C4" t="n">
-        <v>54.42023874180919</v>
+        <v>119.8036540969425</v>
       </c>
       <c r="D4" t="n">
-        <v>59.88268296823845</v>
+        <v>59.41046232249573</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.44233591292137</v>
+        <v>21.57390580082366</v>
       </c>
       <c r="C5" t="n">
-        <v>60.96653243372694</v>
+        <v>101.4390815413017</v>
       </c>
       <c r="D5" t="n">
-        <v>41.89608327873264</v>
+        <v>36.76645152404306</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.52083467153211</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>70.88316599432396</v>
+        <v>68.42781498600269</v>
       </c>
       <c r="D6" t="n">
-        <v>36.22649028670731</v>
+        <v>24.99627829782805</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.3919226226395</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>60.12615639889166</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>27.24840753137022</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>38.7201294554942</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.06874770149305</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.513145251554567</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.34031354932183</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.513145251554567</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
